--- a/output/pdf_financials_xlsx/FVI.xlsx
+++ b/output/pdf_financials_xlsx/FVI.xlsx
@@ -6185,34 +6185,34 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>14.977</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>16.092</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>16.015</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>18.946</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>26.094</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>28.785</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>29.929</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>25.342</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>57.772</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>63.694</v>
       </c>
     </row>
     <row r="93">
@@ -11025,7 +11025,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -20262,7 +20266,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/FVI.xlsx
+++ b/output/pdf_financials_xlsx/FVI.xlsx
@@ -1114,7 +1114,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.493</v>
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>26.975</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>27.513</v>
+        <v>27.02</v>
       </c>
       <c r="F27" s="1" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>33.437</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>36.934</v>
+        <v>36.441</v>
       </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>49.87306902884303</v>
+        <v>49.20735659500918</v>
       </c>
       <c r="F30" s="1" t="inlineStr">
         <is>
@@ -2625,10 +2625,8 @@
           <t xml:space="preserve">    Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B34" s="3" t="n">
+        <v>29.454</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>30.763</v>
@@ -2745,10 +2743,8 @@
           <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B36" s="3" t="n">
+        <v>29.454</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>36.797</v>
@@ -35502,7 +35498,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E267" s="5" t="n">
@@ -78838,7 +78834,7 @@
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E703" t="inlineStr">
